--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-05</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -895,7 +895,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200119.4.101.6</t>
+    <t>http://medis.or.jp/CodeSystem/master-disease-exCode</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1034,7 +1034,7 @@
     <t>Condition.code.coding:medisRecordNo.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200119.4.101.2</t>
+    <t>http://medis.or.jp/CodeSystem/master-disease-keyNumber</t>
   </si>
   <si>
     <t>Condition.code.coding:medisRecordNo.version</t>
@@ -1076,7 +1076,7 @@
     <t>Condition.code.coding:receipt.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ConditionDiseaseCodeReceipt_CS</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/masterB-disease</t>
   </si>
   <si>
     <t>Condition.code.coding:receipt.version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -1118,7 +1118,7 @@
     <t>Condition.code.coding:icd10.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ConditionDiseaseCodeICD10_CS</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/ICD10-2013-full</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10.version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -859,10 +859,10 @@
     <t>MEDIS ICD10対応標準病名マスターの管理番号。</t>
   </si>
   <si>
-    <t>JP_ConditionDiseaseCodeMEDISExchange_VSの中から適切なコードを指定する。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionDiseaseCodeMEDISExchange_VS</t>
+    <t>JP_Disease_MEDIS_Concept_VSの中から適切なコードを指定する。</t>
+  </si>
+  <si>
+    <t>http://medis.or.jp/ValueSet/master-disease-exCode</t>
   </si>
   <si>
     <t>Condition.code.coding:medisExchange.id</t>
@@ -1019,10 +1019,10 @@
     <t>MEDIS ICD10対応標準病名マスター(管理番号)。【詳細参照】</t>
   </si>
   <si>
-    <t>JP_ConditionDiseaseCodeMEDISRecordNo_VSの中から適切なコードを指定する。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionDiseaseCodeMEDISRecordNo_VS</t>
+    <t>JP_Disease_MEDIS_ManagementID_VSの中から適切なコードを指定する。</t>
+  </si>
+  <si>
+    <t>http://medis.or.jp/ValueSet/master-disease-keyNumber</t>
   </si>
   <si>
     <t>Condition.code.coding:medisRecordNo.id</t>
@@ -1061,10 +1061,10 @@
     <t>レセプト電算用傷病名マスター。</t>
   </si>
   <si>
-    <t>JP_ConditionDiseaseCodeReceipt_VSの中から適切なコードを指定する。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionDiseaseCodeReceipt_VS</t>
+    <t>JP_Disease_Claim_VSの中から適切なコードを指定する。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/masterB-disease</t>
   </si>
   <si>
     <t>Condition.code.coding:receipt.id</t>
@@ -1910,7 +1910,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="39.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="490">
   <si>
     <t>Property</t>
   </si>
@@ -1106,7 +1106,7 @@
     <t>JP_ConditionDiseaseCodeICD10_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionDiseaseCodeICD10_VS</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/ICD10-2013-full</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10.id</t>
@@ -1116,9 +1116,6 @@
   </si>
   <si>
     <t>Condition.code.coding:icd10.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/ICD10-2013-full</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10.version</t>
@@ -1910,7 +1907,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="39.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.6953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -7869,7 +7866,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>80</v>
@@ -7946,7 +7943,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>281</v>
@@ -8066,7 +8063,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>289</v>
@@ -8186,7 +8183,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>297</v>
@@ -8306,7 +8303,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>305</v>
@@ -8428,10 +8425,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8457,16 +8454,16 @@
         <v>228</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8515,7 +8512,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8536,10 +8533,10 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8550,10 +8547,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8579,13 +8576,13 @@
         <v>168</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8614,11 +8611,11 @@
         <v>218</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8635,7 +8632,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8653,31 +8650,31 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8696,17 +8693,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8755,7 +8752,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -8770,19 +8767,19 @@
         <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8790,10 +8787,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8816,16 +8813,16 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8875,7 +8872,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8890,19 +8887,19 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -8910,10 +8907,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8936,16 +8933,16 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8995,7 +8992,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9010,19 +9007,19 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9030,10 +9027,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9056,16 +9053,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9115,7 +9112,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9124,7 +9121,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9139,10 +9136,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9150,10 +9147,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9176,13 +9173,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9233,7 +9230,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9254,13 +9251,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9268,10 +9265,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9294,13 +9291,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9351,7 +9348,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9375,10 +9372,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9386,10 +9383,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9412,13 +9409,13 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9469,7 +9466,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9490,13 +9487,13 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9504,10 +9501,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9530,13 +9527,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9587,7 +9584,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9599,19 +9596,19 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9622,10 +9619,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9651,10 +9648,10 @@
         <v>228</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9740,10 +9737,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9769,10 +9766,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>155</v>
@@ -9860,14 +9857,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9889,10 +9886,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>155</v>
@@ -9947,7 +9944,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9982,10 +9979,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10011,10 +10008,10 @@
         <v>168</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10044,11 +10041,11 @@
         <v>218</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10065,7 +10062,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10074,7 +10071,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10083,7 +10080,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>178</v>
@@ -10100,10 +10097,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10126,13 +10123,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10183,7 +10180,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10192,7 +10189,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>104</v>
@@ -10207,7 +10204,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10218,10 +10215,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10247,10 +10244,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10280,11 +10277,11 @@
         <v>218</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10301,7 +10298,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10325,7 +10322,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10336,10 +10333,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10362,16 +10359,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10421,7 +10418,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10433,19 +10430,19 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10456,10 +10453,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10485,10 +10482,10 @@
         <v>228</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10574,10 +10571,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10603,10 +10600,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>155</v>
@@ -10694,14 +10691,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10723,10 +10720,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>155</v>
@@ -10781,7 +10778,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10816,10 +10813,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10845,10 +10842,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10878,11 +10875,11 @@
         <v>218</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
       </c>
@@ -10899,7 +10896,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10908,13 +10905,13 @@
         <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>198</v>
@@ -10923,10 +10920,10 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -10934,10 +10931,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10960,13 +10957,13 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11017,7 +11014,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11026,7 +11023,7 @@
         <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>104</v>
@@ -11041,10 +11038,10 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -11052,10 +11049,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11078,13 +11075,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11135,7 +11132,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11150,16 +11147,16 @@
         <v>104</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AL77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -1106,16 +1106,19 @@
     <t>JP_ConditionDiseaseCodeICD10_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/ICD10-2013-full</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:icd10.id</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:icd10.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:icd10.system</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/ICD10-2013-full</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:icd10.id</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:icd10.extension</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:icd10.system</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10.version</t>
@@ -1907,7 +1910,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="39.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.6953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -7866,7 +7869,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>80</v>
@@ -7943,7 +7946,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>281</v>
@@ -8063,7 +8066,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>289</v>
@@ -8183,7 +8186,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>297</v>
@@ -8303,7 +8306,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>305</v>
@@ -8425,10 +8428,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8454,16 +8457,16 @@
         <v>228</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8512,7 +8515,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8533,10 +8536,10 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8547,10 +8550,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8576,13 +8579,13 @@
         <v>168</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8611,10 +8614,10 @@
         <v>218</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8632,7 +8635,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8650,31 +8653,31 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8693,17 +8696,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8752,7 +8755,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -8767,19 +8770,19 @@
         <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8787,10 +8790,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8813,16 +8816,16 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8872,7 +8875,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8887,19 +8890,19 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -8907,10 +8910,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8933,16 +8936,16 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8992,7 +8995,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9007,19 +9010,19 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9027,10 +9030,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9053,16 +9056,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9112,7 +9115,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9121,7 +9124,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9136,10 +9139,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9147,10 +9150,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9173,13 +9176,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9230,7 +9233,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9251,13 +9254,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9265,10 +9268,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9291,13 +9294,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9348,7 +9351,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9372,10 +9375,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9383,10 +9386,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9409,13 +9412,13 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9466,7 +9469,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9487,13 +9490,13 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9501,10 +9504,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9527,13 +9530,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9584,7 +9587,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9596,7 +9599,7 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
@@ -9608,7 +9611,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9619,10 +9622,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9648,10 +9651,10 @@
         <v>228</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9737,10 +9740,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9766,10 +9769,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>155</v>
@@ -9857,14 +9860,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9886,10 +9889,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>155</v>
@@ -9944,7 +9947,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9979,10 +9982,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10008,10 +10011,10 @@
         <v>168</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10041,10 +10044,10 @@
         <v>218</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10062,7 +10065,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10071,7 +10074,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10080,7 +10083,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>178</v>
@@ -10097,10 +10100,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10123,13 +10126,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10180,7 +10183,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10189,7 +10192,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>104</v>
@@ -10204,7 +10207,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10215,10 +10218,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10244,10 +10247,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10277,10 +10280,10 @@
         <v>218</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10298,7 +10301,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10322,7 +10325,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10333,10 +10336,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10359,16 +10362,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10418,7 +10421,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10430,7 +10433,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10442,7 +10445,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10453,10 +10456,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10482,10 +10485,10 @@
         <v>228</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10571,10 +10574,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10600,10 +10603,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>155</v>
@@ -10691,14 +10694,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10720,10 +10723,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>155</v>
@@ -10778,7 +10781,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10813,10 +10816,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10842,10 +10845,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10875,10 +10878,10 @@
         <v>218</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10896,7 +10899,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10905,13 +10908,13 @@
         <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>198</v>
@@ -10920,10 +10923,10 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -10931,10 +10934,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10957,13 +10960,13 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11014,7 +11017,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11023,7 +11026,7 @@
         <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>104</v>
@@ -11038,10 +11041,10 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -11049,10 +11052,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11075,13 +11078,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11132,7 +11135,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11147,16 +11150,16 @@
         <v>104</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -278,8 +278,8 @@
 健康上の懸念となるレベルに達した、身体的、精神的、社会的な負の状態(condition)や問題（problem／issue）、医療者による診断(diagnosis)、生じたイベント(event)、置かれている状況(situation)、臨床的概念(clinical concept)。</t>
   </si>
   <si>
-    <t>con-3:「verificationStatus」が「entered-in-error」でなく、「category」が「problem-list-item」である場合、「condition.clinicalStatus」が存在している必要があります。」 {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
-con-4:もし状態が軽減された場合、臨床状態は不活動、解決、または寛解でなければなりません。 {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:「verificationStatusがentered-in-errorである場合、condition.clinicalStatusは存在してはなりません。」 {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+    <t>con-3:verificationStatus」が「entered-in-error」でなく、「category」が「problem-list-item」である場合、「condition.clinicalStatus」が存在している必要があります。 {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
+con-4:もし状態が軽減された場合、臨床状態は不活動、解決、または寛解でなければなりません。 {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:verificationStatusがentered-in-errorである場合、condition.clinicalStatusは存在してはなりません。 {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -310,10 +310,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -326,10 +326,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -349,7 +349,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -365,10 +365,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -377,7 +377,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -400,7 +400,7 @@
     <t>Text summary of the resource, for human interpretation. このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -423,13 +423,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -462,7 +462,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.extension:diseaseOutcome</t>
@@ -486,7 +486,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -500,7 +500,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -522,10 +522,10 @@
     <t>この状態の外部ID。</t>
   </si>
   <si>
-    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネス識別子が、この状態に対して一定の値を保持します。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません（[discussion]（resource.html＃identifiers）を参照）。 識別子が単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じ識別子を持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。</t>
+    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネスidentifierが、この状態に対して一定の値を保持します。</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[discussion]（resource.html＃identifiers）を参照）。 identifierが単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じidentifierを持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。</t>
   </si>
   <si>
     <t>Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -599,7 +599,7 @@
     <t>疑い病名を指定するのに使用する。疑い病名の場合は 'unconfirmed'を、確定病名の場合は'confirmed'をそれぞれ指定する。</t>
   </si>
   <si>
-    <t>「状態や診断の臨床状況を支持または拒否するための検証状況」</t>
+    <t>状態や診断の臨床状況を支持または拒否するための検証状況</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-ver-status|4.0.1</t>
@@ -628,7 +628,7 @@
     <t>problem-list-item | encounter-diagnosis（プロブレムリスト | 一時的な診断）</t>
   </si>
   <si>
-    <t>「状態に割り当てられたカテゴリー。」</t>
+    <t>状態に割り当てられたカテゴリー。</t>
   </si>
   <si>
     <t>分類はしばしば文脈に強く依存しており、他の文脈では区別が不十分であるか、あまり役に立たないように見えることがあります。</t>
@@ -707,7 +707,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「状態や診断の特定」(Joutai ya shindan no tokutei)</t>
+    <t>状態や診断の特定</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code</t>
@@ -837,7 +837,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -1166,7 +1166,7 @@
     <t>この症状が現れる解剖学的位置。</t>
   </si>
   <si>
-    <t>「Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。」</t>
+    <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
@@ -1198,7 +1198,7 @@
     <t>Who has the condition? 誰がこの状態を有するか</t>
   </si>
   <si>
-    <t>「その病状記録が関連する患者またはグループを示します。」</t>
+    <t>その病状記録が関連する患者またはグループを示します。</t>
   </si>
   <si>
     <t>Group is typically used for veterinary or public health use cases.</t>
@@ -1230,7 +1230,7 @@
 この患者状態の記録やレコード作成に関連する受療の状況（外来、入院、救急、在宅など）</t>
   </si>
   <si>
-    <t>通常、イベントが発生した出会いの中で行われることが多いですが、公式的に出会いが完了する前または後に開始される場合がありますが、それでも出会いの文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初の出会いとは異なる場合があります。</t>
+    <t>通常、イベントが発生したEncounter（診察、受診、入退院など）の中で行われることが多いですが、公式的にEncounter（診察、受診、入退院など）が完了する前または後に開始される場合がありますが、それでもEncounter（診察、受診、入退院など）の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初のEncounter（診察、受診、入退院など）とは異なる場合があります。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1397,7 +1397,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>Condition.stage.modifierExtension</t>
@@ -1407,11 +1407,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」(Ninshiki sarenakutemo mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1423,10 +1423,10 @@
     <t>簡単な要約（病気特有のもの）</t>
   </si>
   <si>
-    <t>「ステージ3」といった、単純なステージの概要。ステージの決定は病気によって異なります。」</t>
-  </si>
-  <si>
-    <t>「状態段階を説明するコード（例：がんの段階）」</t>
+    <t>ステージ3」といった、単純なステージの概要。ステージの決定は病気によって異なります。</t>
+  </si>
+  <si>
+    <t>状態段階を説明するコード（例：がんの段階）</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
@@ -1446,10 +1446,10 @@
 </t>
   </si>
   <si>
-    <t>「評価の公式記録」(Hyōka no kōshiki kiroku)</t>
-  </si>
-  <si>
-    <t>「ステージング評価の根拠となる正式な証拠記録への参照。」</t>
+    <t>「評価の公式記録」</t>
+  </si>
+  <si>
+    <t>ステージング評価の根拠となる正式な証拠記録への参照。</t>
   </si>
   <si>
     <t>.self</t>
@@ -1461,7 +1461,7 @@
     <t>"演出の種類" (Enshutsu no shurui)</t>
   </si>
   <si>
-    <t>「病理的ステージングや臨床ステージングといった種類のステージング」</t>
+    <t>病理的ステージングや臨床ステージングといった種類のステージング</t>
   </si>
   <si>
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
@@ -1483,7 +1483,7 @@
 患者状態を確認または否定した証拠など、状態の検証ステータスの裏付けとなる症状や兆候。</t>
   </si>
   <si>
-    <t>「証拠は、コード化された症状/症状の簡単なリスト、または観察や正式な評価への言及、またはその両方である可能性があります。」</t>
+    <t>証拠は、コード化された症状/症状の簡単なリスト、または観察や正式な評価への言及、またはその両方である可能性があります。</t>
   </si>
   <si>
     <t>con-2:証拠にはコードまたは詳細が必要です。 {code.exists() or detail.exists()}
@@ -1508,7 +1508,7 @@
     <t>表れ/症状</t>
   </si>
   <si>
-    <t>「この状態の記録に至った兆候や症状。」</t>
+    <t>この状態の記録に至った兆候や症状。</t>
   </si>
   <si>
     <t>症状や現れ方を記述するコード。</t>
@@ -1537,7 +1537,7 @@
 </t>
   </si>
   <si>
-    <t>「別の場所で見つかったサポート情報」</t>
+    <t>別の場所で見つかったサポート情報</t>
   </si>
   <si>
     <t>その他関連情報、病理検査報告書などのリンク。</t>
@@ -1909,7 +1909,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="39.1328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2963" uniqueCount="490">
   <si>
     <t>Property</t>
   </si>
@@ -1169,10 +1169,7 @@
     <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
-    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1909,8 +1906,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.6171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.75" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -8613,11 +8610,9 @@
       <c r="X56" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="Y56" t="s" s="2">
+      <c r="Y56" s="2"/>
+      <c r="Z56" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8653,31 +8648,31 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8696,17 +8691,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8755,7 +8750,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -8770,19 +8765,19 @@
         <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8790,10 +8785,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8816,16 +8811,16 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8875,7 +8870,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8890,19 +8885,19 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -8910,10 +8905,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8936,16 +8931,16 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8995,7 +8990,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9010,19 +9005,19 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9030,10 +9025,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9056,16 +9051,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9115,7 +9110,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9124,7 +9119,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9139,10 +9134,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9150,10 +9145,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9176,13 +9171,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9233,7 +9228,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9254,13 +9249,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9268,10 +9263,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9294,13 +9289,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9351,7 +9346,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9375,10 +9370,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9386,10 +9381,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9412,13 +9407,13 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9469,7 +9464,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9490,13 +9485,13 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9504,10 +9499,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9530,13 +9525,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9587,7 +9582,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9599,19 +9594,19 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9622,10 +9617,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9651,10 +9646,10 @@
         <v>228</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9740,10 +9735,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9769,10 +9764,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>155</v>
@@ -9860,14 +9855,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9889,10 +9884,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>155</v>
@@ -9947,7 +9942,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9982,10 +9977,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10011,10 +10006,10 @@
         <v>168</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10044,11 +10039,11 @@
         <v>218</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10065,7 +10060,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10074,7 +10069,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10083,7 +10078,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>178</v>
@@ -10100,10 +10095,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10126,13 +10121,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10183,7 +10178,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10192,7 +10187,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>104</v>
@@ -10207,7 +10202,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10218,10 +10213,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10247,10 +10242,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10280,11 +10275,11 @@
         <v>218</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10301,7 +10296,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10325,7 +10320,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10336,10 +10331,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10362,16 +10357,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10421,7 +10416,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10433,19 +10428,19 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10456,10 +10451,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10485,10 +10480,10 @@
         <v>228</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10574,10 +10569,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10603,10 +10598,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>155</v>
@@ -10694,14 +10689,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10723,10 +10718,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>155</v>
@@ -10781,7 +10776,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10816,10 +10811,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10845,10 +10840,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10878,11 +10873,11 @@
         <v>218</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
       </c>
@@ -10899,7 +10894,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10908,13 +10903,13 @@
         <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>198</v>
@@ -10923,10 +10918,10 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -10934,10 +10929,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10960,13 +10955,13 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11017,7 +11012,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11026,7 +11021,7 @@
         <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>104</v>
@@ -11041,10 +11036,10 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -11052,10 +11047,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11078,13 +11073,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11135,7 +11130,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11150,16 +11145,16 @@
         <v>104</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AL77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -278,8 +278,8 @@
 健康上の懸念となるレベルに達した、身体的、精神的、社会的な負の状態(condition)や問題（problem／issue）、医療者による診断(diagnosis)、生じたイベント(event)、置かれている状況(situation)、臨床的概念(clinical concept)。</t>
   </si>
   <si>
-    <t>con-3:verificationStatus」が「entered-in-error」でなく、「category」が「problem-list-item」である場合、「condition.clinicalStatus」が存在している必要があります。 {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
-con-4:もし状態が軽減された場合、臨床状態は不活動、解決、または寛解でなければなりません。 {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:verificationStatusがentered-in-errorである場合、condition.clinicalStatusは存在してはなりません。 {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
+    <t>con-3:「verificationStatus」が「entered-in-error」でなく、「category」が「problem-list-item」である場合、「condition.clinicalStatus」が存在している必要があります。」 {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
+con-4:もし状態が軽減された場合、臨床状態は不活動、解決、または寛解でなければなりません。 {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:「verificationStatusがentered-in-errorである場合、condition.clinicalStatusは存在してはなりません。」 {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -310,10 +310,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
-  </si>
-  <si>
-    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
+    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
+  </si>
+  <si>
+    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -326,10 +326,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata</t>
-  </si>
-  <si>
-    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>「リソースに関するメタデータ」</t>
+  </si>
+  <si>
+    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -349,7 +349,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
+    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -368,7 +368,7 @@
     <t>「リソースコンテンツの言語」</t>
   </si>
   <si>
-    <t>リソースが書かれている基本言語。</t>
+    <t>「リソースが書かれている基本言語。」</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -400,7 +400,7 @@
     <t>Text summary of the resource, for human interpretation. このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
-    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
+    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -426,10 +426,10 @@
     <t>「含まれている、インラインのリソース」</t>
   </si>
   <si>
-    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
-  </si>
-  <si>
-    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
+    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
+  </si>
+  <si>
+    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -462,7 +462,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.extension:diseaseOutcome</t>
@@ -497,10 +497,10 @@
 user content</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
+    <t xml:space="preserve">無視できない拡張機能 </t>
+  </si>
+  <si>
+    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -522,10 +522,10 @@
     <t>この状態の外部ID。</t>
   </si>
   <si>
-    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネスidentifierが、この状態に対して一定の値を保持します。</t>
-  </si>
-  <si>
-    <t>これはビジネスidentifierであり、リソースidentifierではありません（[discussion]（resource.html＃identifiers）を参照）。 identifierが単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じidentifierを持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。</t>
+    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネス識別子が、この状態に対して一定の値を保持します。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません（[discussion]（resource.html＃identifiers）を参照）。 識別子が単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じ識別子を持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。</t>
   </si>
   <si>
     <t>Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -599,7 +599,7 @@
     <t>疑い病名を指定するのに使用する。疑い病名の場合は 'unconfirmed'を、確定病名の場合は'confirmed'をそれぞれ指定する。</t>
   </si>
   <si>
-    <t>状態や診断の臨床状況を支持または拒否するための検証状況</t>
+    <t>「状態や診断の臨床状況を支持または拒否するための検証状況」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-ver-status|4.0.1</t>
@@ -628,7 +628,7 @@
     <t>problem-list-item | encounter-diagnosis（プロブレムリスト | 一時的な診断）</t>
   </si>
   <si>
-    <t>状態に割り当てられたカテゴリー。</t>
+    <t>「状態に割り当てられたカテゴリー。」</t>
   </si>
   <si>
     <t>分類はしばしば文脈に強く依存しており、他の文脈では区別が不十分であるか、あまり役に立たないように見えることがあります。</t>
@@ -707,7 +707,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>状態や診断の特定</t>
+    <t>「状態や診断の特定」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code</t>
@@ -1166,7 +1166,7 @@
     <t>この症状が現れる解剖学的位置。</t>
   </si>
   <si>
-    <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
+    <t>「Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。」</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
@@ -1195,7 +1195,7 @@
     <t>Who has the condition? 誰がこの状態を有するか</t>
   </si>
   <si>
-    <t>その病状記録が関連する患者またはグループを示します。</t>
+    <t>「その病状記録が関連する患者またはグループを示します。」</t>
   </si>
   <si>
     <t>Group is typically used for veterinary or public health use cases.</t>
@@ -1227,7 +1227,7 @@
 この患者状態の記録やレコード作成に関連する受療の状況（外来、入院、救急、在宅など）</t>
   </si>
   <si>
-    <t>通常、イベントが発生したEncounter（診察、受診、入退院など）の中で行われることが多いですが、公式的にEncounter（診察、受診、入退院など）が完了する前または後に開始される場合がありますが、それでもEncounter（診察、受診、入退院など）の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初のEncounter（診察、受診、入退院など）とは異なる場合があります。</t>
+    <t>通常、イベントが発生した出会いの中で行われることが多いですが、公式的に出会いが完了する前または後に開始される場合がありますが、それでも出会いの文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初の出会いとは異なる場合があります。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1394,7 +1394,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
+    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
   </si>
   <si>
     <t>Condition.stage.modifierExtension</t>
@@ -1404,11 +1404,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>認識されなくても無視できない拡張機能</t>
-  </si>
-  <si>
-    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
+    <t>「認識されなくても無視できない拡張機能」</t>
+  </si>
+  <si>
+    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1420,10 +1420,10 @@
     <t>簡単な要約（病気特有のもの）</t>
   </si>
   <si>
-    <t>ステージ3」といった、単純なステージの概要。ステージの決定は病気によって異なります。</t>
-  </si>
-  <si>
-    <t>状態段階を説明するコード（例：がんの段階）</t>
+    <t>「ステージ3」といった、単純なステージの概要。ステージの決定は病気によって異なります。」</t>
+  </si>
+  <si>
+    <t>「状態段階を説明するコード（例：がんの段階）」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
@@ -1446,7 +1446,7 @@
     <t>「評価の公式記録」</t>
   </si>
   <si>
-    <t>ステージング評価の根拠となる正式な証拠記録への参照。</t>
+    <t>「ステージング評価の根拠となる正式な証拠記録への参照。」</t>
   </si>
   <si>
     <t>.self</t>
@@ -1458,7 +1458,7 @@
     <t>"演出の種類" (Enshutsu no shurui)</t>
   </si>
   <si>
-    <t>病理的ステージングや臨床ステージングといった種類のステージング</t>
+    <t>「病理的ステージングや臨床ステージングといった種類のステージング」</t>
   </si>
   <si>
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
@@ -1480,7 +1480,7 @@
 患者状態を確認または否定した証拠など、状態の検証ステータスの裏付けとなる症状や兆候。</t>
   </si>
   <si>
-    <t>証拠は、コード化された症状/症状の簡単なリスト、または観察や正式な評価への言及、またはその両方である可能性があります。</t>
+    <t>「証拠は、コード化された症状/症状の簡単なリスト、または観察や正式な評価への言及、またはその両方である可能性があります。」</t>
   </si>
   <si>
     <t>con-2:証拠にはコードまたは詳細が必要です。 {code.exists() or detail.exists()}
@@ -1505,7 +1505,7 @@
     <t>表れ/症状</t>
   </si>
   <si>
-    <t>この状態の記録に至った兆候や症状。</t>
+    <t>「この状態の記録に至った兆候や症状。」</t>
   </si>
   <si>
     <t>症状や現れ方を記述するコード。</t>
@@ -1534,7 +1534,7 @@
 </t>
   </si>
   <si>
-    <t>別の場所で見つかったサポート情報</t>
+    <t>「別の場所で見つかったサポート情報」</t>
   </si>
   <si>
     <t>その他関連情報、病理検査報告書などのリンク。</t>
@@ -1906,7 +1906,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="30.75" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="32.94921875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -278,8 +278,8 @@
 健康上の懸念となるレベルに達した、身体的、精神的、社会的な負の状態(condition)や問題（problem／issue）、医療者による診断(diagnosis)、生じたイベント(event)、置かれている状況(situation)、臨床的概念(clinical concept)。</t>
   </si>
   <si>
-    <t>con-3:「verificationStatus」が「entered-in-error」でなく、「category」が「problem-list-item」である場合、「condition.clinicalStatus」が存在している必要があります。」 {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
-con-4:もし状態が軽減された場合、臨床状態は不活動、解決、または寛解でなければなりません。 {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:「verificationStatusがentered-in-errorである場合、condition.clinicalStatusは存在してはなりません。」 {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+    <t>con-3:verificationStatus」が「entered-in-error」でなく、「category」が「problem-list-item」である場合、「condition.clinicalStatus」が存在している必要があります。 {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
+con-4:もし状態が軽減された場合、臨床状態は不活動、解決、または寛解でなければなりません。 {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:verificationStatusがentered-in-errorである場合、condition.clinicalStatusは存在してはなりません。 {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -310,10 +310,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -326,10 +326,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -349,7 +349,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -365,10 +365,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>リソースコンテンツの言語</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -377,7 +377,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -400,7 +400,7 @@
     <t>Text summary of the resource, for human interpretation. このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -423,13 +423,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>含まれている、インラインのリソース</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -462,7 +462,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.extension:diseaseOutcome</t>
@@ -497,10 +497,10 @@
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">無視できない拡張機能 </t>
-  </si>
-  <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -522,10 +522,10 @@
     <t>この状態の外部ID。</t>
   </si>
   <si>
-    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネス識別子が、この状態に対して一定の値を保持します。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません（[discussion]（resource.html＃identifiers）を参照）。 識別子が単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じ識別子を持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。</t>
+    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネスidentifierが、この状態に対して一定の値を保持します。</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[discussion]（resource.html＃identifiers）を参照）。 identifierが単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じidentifierを持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。</t>
   </si>
   <si>
     <t>Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -599,7 +599,7 @@
     <t>疑い病名を指定するのに使用する。疑い病名の場合は 'unconfirmed'を、確定病名の場合は'confirmed'をそれぞれ指定する。</t>
   </si>
   <si>
-    <t>「状態や診断の臨床状況を支持または拒否するための検証状況」</t>
+    <t>状態や診断の臨床状況を支持または拒否するための検証状況</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-ver-status|4.0.1</t>
@@ -628,7 +628,7 @@
     <t>problem-list-item | encounter-diagnosis（プロブレムリスト | 一時的な診断）</t>
   </si>
   <si>
-    <t>「状態に割り当てられたカテゴリー。」</t>
+    <t>状態に割り当てられたカテゴリー。</t>
   </si>
   <si>
     <t>分類はしばしば文脈に強く依存しており、他の文脈では区別が不十分であるか、あまり役に立たないように見えることがあります。</t>
@@ -707,7 +707,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「状態や診断の特定」</t>
+    <t>状態や診断の特定</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code</t>
@@ -1166,7 +1166,7 @@
     <t>この症状が現れる解剖学的位置。</t>
   </si>
   <si>
-    <t>「Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。」</t>
+    <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
@@ -1195,7 +1195,7 @@
     <t>Who has the condition? 誰がこの状態を有するか</t>
   </si>
   <si>
-    <t>「その病状記録が関連する患者またはグループを示します。」</t>
+    <t>その病状記録が関連する患者またはグループを示します。</t>
   </si>
   <si>
     <t>Group is typically used for veterinary or public health use cases.</t>
@@ -1227,7 +1227,7 @@
 この患者状態の記録やレコード作成に関連する受療の状況（外来、入院、救急、在宅など）</t>
   </si>
   <si>
-    <t>通常、イベントが発生した出会いの中で行われることが多いですが、公式的に出会いが完了する前または後に開始される場合がありますが、それでも出会いの文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初の出会いとは異なる場合があります。</t>
+    <t>通常、イベントが発生したEncounter（診察、受診、入退院など）の中で行われることが多いですが、公式的にEncounter（診察、受診、入退院など）が完了する前または後に開始される場合がありますが、それでもEncounter（診察、受診、入退院など）の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初のEncounter（診察、受診、入退院など）とは異なる場合があります。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1394,7 +1394,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>Condition.stage.modifierExtension</t>
@@ -1404,11 +1404,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1420,10 +1420,10 @@
     <t>簡単な要約（病気特有のもの）</t>
   </si>
   <si>
-    <t>「ステージ3」といった、単純なステージの概要。ステージの決定は病気によって異なります。」</t>
-  </si>
-  <si>
-    <t>「状態段階を説明するコード（例：がんの段階）」</t>
+    <t>ステージ3」といった、単純なステージの概要。ステージの決定は病気によって異なります。</t>
+  </si>
+  <si>
+    <t>状態段階を説明するコード（例：がんの段階）</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
@@ -1443,10 +1443,10 @@
 </t>
   </si>
   <si>
-    <t>「評価の公式記録」</t>
-  </si>
-  <si>
-    <t>「ステージング評価の根拠となる正式な証拠記録への参照。」</t>
+    <t>評価の公式記録</t>
+  </si>
+  <si>
+    <t>ステージング評価の根拠となる正式な証拠記録への参照。</t>
   </si>
   <si>
     <t>.self</t>
@@ -1455,10 +1455,10 @@
     <t>Condition.stage.type</t>
   </si>
   <si>
-    <t>"演出の種類" (Enshutsu no shurui)</t>
-  </si>
-  <si>
-    <t>「病理的ステージングや臨床ステージングといった種類のステージング」</t>
+    <t>演出の種類</t>
+  </si>
+  <si>
+    <t>病理的ステージングや臨床ステージングといった種類のステージング</t>
   </si>
   <si>
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
@@ -1480,7 +1480,7 @@
 患者状態を確認または否定した証拠など、状態の検証ステータスの裏付けとなる症状や兆候。</t>
   </si>
   <si>
-    <t>「証拠は、コード化された症状/症状の簡単なリスト、または観察や正式な評価への言及、またはその両方である可能性があります。」</t>
+    <t>証拠は、コード化された症状/症状の簡単なリスト、または観察や正式な評価への言及、またはその両方である可能性があります。</t>
   </si>
   <si>
     <t>con-2:証拠にはコードまたは詳細が必要です。 {code.exists() or detail.exists()}
@@ -1505,7 +1505,7 @@
     <t>表れ/症状</t>
   </si>
   <si>
-    <t>「この状態の記録に至った兆候や症状。」</t>
+    <t>この状態の記録に至った兆候や症状。</t>
   </si>
   <si>
     <t>症状や現れ方を記述するコード。</t>
@@ -1534,7 +1534,7 @@
 </t>
   </si>
   <si>
-    <t>「別の場所で見つかったサポート情報」</t>
+    <t>別の場所で見つかったサポート情報</t>
   </si>
   <si>
     <t>その他関連情報、病理検査報告書などのリンク。</t>
@@ -1906,7 +1906,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="32.94921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.75" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -462,7 +462,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.extension:diseaseOutcome</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -1016,7 +1016,7 @@
     <t>medisRecordNo</t>
   </si>
   <si>
-    <t>MEDIS ICD10対応標準病名マスター(管理番号)。【詳細参照】</t>
+    <t>MEDIS ICD10対応標準病名マスターの交換用コード。</t>
   </si>
   <si>
     <t>JP_Disease_MEDIS_ManagementID_VSの中から適切なコードを指定する。</t>
@@ -5567,7 +5567,7 @@
         <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>317</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1502,10 +1502,10 @@
     <t>Condition.evidence.code</t>
   </si>
   <si>
-    <t>表れ/症状</t>
-  </si>
-  <si>
-    <t>この状態の記録に至った兆候や症状。</t>
+    <t>徴候や症状</t>
+  </si>
+  <si>
+    <t>この状態の記録に至った徴候や症状。</t>
   </si>
   <si>
     <t>症状や現れ方を記述するコード。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -554,7 +554,7 @@
 この患者状態の臨床的ステータス（アクティブか否かなど）</t>
   </si>
   <si>
-    <t>診断の場合、転帰区分を指定するのに使用する。使用する場合、ConditionClinicalStatusCodesは必須で、それ以外にHL7表0241、JHSD表0006、レセプト電算システム転帰区分コードが使用できる。</t>
+    <t>データ型はCodeableConceptである。clinicalStatusには何らかの臨床的判断が伴うため、FHIRで指定されたvalue setよりも特異性のあるvalue setが必要となりうる。これは、いわゆる転帰(outcome)のみを意味しない。使用する場合、ConditionClinicalStatusCodesを必須として指定し、それ以外にHL7表0241、JHSD表0006、レセプト電算システム転帰区分コードが使用できる。</t>
   </si>
   <si>
     <t>required</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -1882,17 +1882,17 @@
   <dimension ref="A1:AP77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.1875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.5625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.16796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="185.2109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1901,28 +1901,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="30.75" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.109375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="26.36328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.24609375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="58.4765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="190.4140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -1227,7 +1227,7 @@
 この患者状態の記録やレコード作成に関連する受療の状況（外来、入院、救急、在宅など）</t>
   </si>
   <si>
-    <t>通常、イベントが発生したEncounter（診察、受診、入退院など）の中で行われることが多いですが、公式的にEncounter（診察、受診、入退院など）が完了する前または後に開始される場合がありますが、それでもEncounter（診察、受診、入退院など）の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初のEncounter（診察、受診、入退院など）とは異なる場合があります。</t>
+    <t>通常、イベントが発生した受療行動の中で行われることが多いですが、公式的に受療行動が完了する前または後に開始される場合がありますが、それでも受療行動の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初の受療行動とは異なる場合があります。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1455,7 +1455,7 @@
     <t>Condition.stage.type</t>
   </si>
   <si>
-    <t>演出の種類</t>
+    <t>ステージングの種類</t>
   </si>
   <si>
     <t>病理的ステージングや臨床ステージングといった種類のステージング</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2963" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -1169,7 +1169,10 @@
     <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Condition_BodySite_VS</t>
+    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1906,8 +1909,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="26.36328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.24609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.96875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -8610,9 +8613,11 @@
       <c r="X56" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="Y56" s="2"/>
+      <c r="Y56" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8648,31 +8653,31 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8691,17 +8696,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8750,7 +8755,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -8765,19 +8770,19 @@
         <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8785,10 +8790,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8811,16 +8816,16 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8870,7 +8875,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8885,19 +8890,19 @@
         <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -8905,10 +8910,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8931,16 +8936,16 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8990,7 +8995,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9005,19 +9010,19 @@
         <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9025,10 +9030,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9051,16 +9056,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9110,7 +9115,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9119,7 +9124,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9134,10 +9139,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9145,10 +9150,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9171,13 +9176,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9228,7 +9233,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9249,13 +9254,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9263,10 +9268,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9289,13 +9294,13 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9346,7 +9351,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9370,10 +9375,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9381,10 +9386,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9407,13 +9412,13 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9464,7 +9469,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9485,13 +9490,13 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9499,10 +9504,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9525,13 +9530,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9582,7 +9587,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9594,7 +9599,7 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
@@ -9606,7 +9611,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9617,10 +9622,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9646,10 +9651,10 @@
         <v>228</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9735,10 +9740,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9764,10 +9769,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>155</v>
@@ -9855,14 +9860,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9884,10 +9889,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>155</v>
@@ -9942,7 +9947,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9977,10 +9982,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10006,10 +10011,10 @@
         <v>168</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10039,10 +10044,10 @@
         <v>218</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10060,7 +10065,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10069,7 +10074,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10078,7 +10083,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>178</v>
@@ -10095,10 +10100,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10121,13 +10126,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10178,7 +10183,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10187,7 +10192,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>104</v>
@@ -10202,7 +10207,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10213,10 +10218,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10242,10 +10247,10 @@
         <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10275,10 +10280,10 @@
         <v>218</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10296,7 +10301,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10320,7 +10325,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10331,10 +10336,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10357,16 +10362,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10416,7 +10421,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10428,7 +10433,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10440,7 +10445,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10451,10 +10456,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10480,10 +10485,10 @@
         <v>228</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10569,10 +10574,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10598,10 +10603,10 @@
         <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>155</v>
@@ -10689,14 +10694,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10718,10 +10723,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>155</v>
@@ -10776,7 +10781,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10811,10 +10816,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10840,10 +10845,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10873,10 +10878,10 @@
         <v>218</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10894,7 +10899,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10903,13 +10908,13 @@
         <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>198</v>
@@ -10918,10 +10923,10 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -10929,10 +10934,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10955,13 +10960,13 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11012,7 +11017,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11021,7 +11026,7 @@
         <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>104</v>
@@ -11036,10 +11041,10 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -11047,10 +11052,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11073,13 +11078,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11130,7 +11135,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11145,16 +11150,16 @@
         <v>104</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -380,7 +380,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -637,7 +637,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -710,7 +710,7 @@
     <t>状態や診断の特定</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1172,7 +1172,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1429,7 +1429,7 @@
     <t>状態段階を説明するコード（例：がんの段階）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1467,7 +1467,7 @@
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1514,7 +1514,7 @@
     <t>症状や現れ方を記述するコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1533,7 +1533,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1910,7 +1910,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.96875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -3850,7 +3850,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>212</v>
       </c>
@@ -11170,12 +11170,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP77">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -853,10 +853,10 @@
     <t>medisExchange</t>
   </si>
   <si>
-    <t>MEDIS ICD10対応標準病名マスター(交換用コード)。【詳細参照】</t>
-  </si>
-  <si>
-    <t>MEDIS ICD10対応標準病名マスターの管理番号。</t>
+    <t>MEDIS ICD10対応標準病名マスターの交換用コード。【詳細参照】</t>
+  </si>
+  <si>
+    <t>MEDIS ICD10対応標準病名マスターの交換用コード。</t>
   </si>
   <si>
     <t>JP_Disease_MEDIS_Concept_VSの中から適切なコードを指定する。</t>
@@ -1016,7 +1016,7 @@
     <t>medisRecordNo</t>
   </si>
   <si>
-    <t>MEDIS ICD10対応標準病名マスターの交換用コード。</t>
+    <t>MEDIS ICD10対応標準病名マスターの管理番号。</t>
   </si>
   <si>
     <t>JP_Disease_MEDIS_ManagementID_VSの中から適切なコードを指定する。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -663,7 +663,7 @@
   </si>
   <si>
     <t>Coding of the severity with a terminology is preferred, where possible.  
-可能な限り、ターミノロジを用いて重症度をコーディングすることが好ましい。  
+可能な限り、ターミノロジを用いて重症度をコード化することが好ましい。  
 このプロファイルではHL70421 Severity of Illness Code（MI 軽度, MO 中度, SE 重度）を採用。</t>
   </si>
   <si>
